--- a/backend/data/financials_by_company/000760.KS.xlsx
+++ b/backend/data/financials_by_company/000760.KS.xlsx
@@ -4264,10 +4264,8 @@
           <t>Seoul</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>04537</t>
-        </is>
+      <c r="D2" t="n">
+        <v>4537</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4515,7 +4513,7 @@
         <v>16334.897</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
         <v>-0.00847</v>
